--- a/SRC_CM_SAP_LOGOFF_E/Config/Resource-SRC_CM_SAP_LOGOFF_E(JA).xlsx
+++ b/SRC_CM_SAP_LOGOFF_E/Config/Resource-SRC_CM_SAP_LOGOFF_E(JA).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_案件\01_Logoff\SRC_CM_SAP_LOGOFF\SRC_CM_SAP_LOGOFF\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UiPathStudioProject\U0011UiPath Foundation pack for Accelerators for SAP ECC\SRC_CM_SAP_LOGOFF_E\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F92C62D-0E4F-4D33-A699-E2F6F463E7F4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53BC043-7CE0-4004-924B-FF554BB0A2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18915" yWindow="1770" windowWidth="21645" windowHeight="9840" xr2:uid="{1D813E3E-3342-4978-A98A-84363F7AA1D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1D813E3E-3342-4978-A98A-84363F7AA1D1}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseSelectors" sheetId="4" r:id="rId1"/>
@@ -62,7 +62,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;wnd app='saplogon.exe' cls='#32770' title='SAP Logon 750' /&gt;</t>
+    <t>&lt;wnd app='saplogon.exe' cls='#32770' title='SAP Logon 770' /&gt;</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -74,14 +74,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -133,7 +133,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -149,9 +149,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -189,7 +189,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -295,7 +295,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -437,7 +437,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -446,12 +446,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DA6B166-A5ED-4C3D-AF8C-F0A985CF78B1}">
   <dimension ref="A1:X861"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="137.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="24" width="7.625" style="2" customWidth="1"/>
-    <col min="25" max="16384" width="12.625" style="2"/>
+    <col min="1" max="1" width="33.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="137.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="24" width="7.5703125" style="2" customWidth="1"/>
+    <col min="25" max="16384" width="12.5703125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="18.75" x14ac:dyDescent="0.3">
@@ -1382,6 +1382,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C827732D69AAF14BA01846CE3CC7794A" ma:contentTypeVersion="9" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="c45483ed6e5ce5006a52541c2b9ecbfd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0bc06b84-8904-4b80-b12f-bdecd9bbb428" xmlns:ns3="5cee1336-4f95-4b7b-89f0-d6c62532513b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1e37752a973e793fedbf688ee3b208e9" ns2:_="" ns3:_="">
     <xsd:import namespace="0bc06b84-8904-4b80-b12f-bdecd9bbb428"/>
@@ -1578,12 +1584,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91400061-949D-46D6-A279-A27207727585}">
   <ds:schemaRefs>
@@ -1593,14 +1593,29 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ED76598-101D-4CB6-B6FA-7CD09DC970B6}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48A98695-63EF-4E79-B620-143750669FD6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ED76598-101D-4CB6-B6FA-7CD09DC970B6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="0bc06b84-8904-4b80-b12f-bdecd9bbb428"/>
+    <ds:schemaRef ds:uri="5cee1336-4f95-4b7b-89f0-d6c62532513b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>